--- a/output/2025_A03_SECCION_A5_TABLAS.xlsx
+++ b/output/2025_A03_SECCION_A5_TABLAS.xlsx
@@ -195,6 +195,9 @@
     <t>nombre_establecimiento</t>
   </si>
   <si>
+    <t>CECOSF Haydeé Sepúlveda</t>
+  </si>
+  <si>
     <t>CECOSF Wilma Yoli Gomez Conejera</t>
   </si>
   <si>
@@ -234,9 +237,6 @@
     <t>Centro Comunitario de Salud Familiar Concejal Guillermo Flores O.</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
-  </si>
-  <si>
     <t>Centro Comunitario de Salud Familiar Dr. Lucas Sierra</t>
   </si>
   <si>
@@ -801,10 +801,10 @@
     <t>CESFAM La Reina de Colina</t>
   </si>
   <si>
+    <t>Hospital Comunitario de Til Til</t>
+  </si>
+  <si>
     <t>Hospital de Curacaví</t>
-  </si>
-  <si>
-    <t>Hospital de Til Til</t>
   </si>
   <si>
     <t>Hospital San José de Maipo</t>
@@ -1334,15 +1334,6 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>3376</v>
-      </c>
-      <c r="C8">
-        <v>5626</v>
-      </c>
-      <c r="D8">
-        <v>60.00710984713828</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2041,13 +2032,13 @@
         <v>57</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>67.3469387755102</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2055,13 +2046,13 @@
         <v>58</v>
       </c>
       <c r="B4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>43.90243902439025</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2069,10 +2060,13 @@
         <v>59</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <v>43.90243902439025</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2080,13 +2074,10 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>91.66666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2094,13 +2085,13 @@
         <v>61</v>
       </c>
       <c r="B7">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>65.21739130434783</v>
+        <v>91.66666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2108,13 +2099,13 @@
         <v>62</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D8">
-        <v>90.90909090909091</v>
+        <v>65.21739130434783</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2122,13 +2113,13 @@
         <v>63</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>70.58823529411765</v>
+        <v>90.90909090909091</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2136,13 +2127,13 @@
         <v>64</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>58.33333333333334</v>
+        <v>70.58823529411765</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2150,13 +2141,13 @@
         <v>65</v>
       </c>
       <c r="B11">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>80.95238095238095</v>
+        <v>58.33333333333334</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2164,13 +2155,13 @@
         <v>66</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>94.11764705882352</v>
+        <v>80.95238095238095</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2178,13 +2169,13 @@
         <v>67</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>94.11764705882352</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2192,13 +2183,13 @@
         <v>68</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>57.14285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2206,13 +2197,13 @@
         <v>69</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>75</v>
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2220,13 +2211,13 @@
         <v>70</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>67.3469387755102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4851,13 +4842,13 @@
         <v>259</v>
       </c>
       <c r="B205">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C205">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="D205">
-        <v>52.38095238095239</v>
+        <v>69.64285714285714</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4865,13 +4856,13 @@
         <v>260</v>
       </c>
       <c r="B206">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C206">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="D206">
-        <v>69.64285714285714</v>
+        <v>52.38095238095239</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5382,15 +5373,6 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>2756</v>
-      </c>
-      <c r="C8">
-        <v>4932</v>
-      </c>
-      <c r="D8">
-        <v>55.87996755879967</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6089,13 +6071,13 @@
         <v>57</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>92.30769230769231</v>
+        <v>62.26415094339622</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6103,13 +6085,13 @@
         <v>58</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>67.74193548387096</v>
+        <v>92.30769230769231</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6117,13 +6099,13 @@
         <v>59</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>67.74193548387096</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6131,13 +6113,13 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6145,13 +6127,13 @@
         <v>61</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>67.24137931034483</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6159,13 +6141,13 @@
         <v>62</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>75</v>
+        <v>67.24137931034483</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6173,13 +6155,13 @@
         <v>63</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>16</v>
       </c>
       <c r="D9">
-        <v>68.75</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6187,13 +6169,13 @@
         <v>64</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>75</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6201,13 +6183,13 @@
         <v>65</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6215,13 +6197,13 @@
         <v>66</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>71.42857142857143</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6229,13 +6211,13 @@
         <v>67</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>71.42857142857143</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6243,13 +6225,13 @@
         <v>68</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6271,13 +6253,13 @@
         <v>70</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>62.26415094339622</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -8905,13 +8887,13 @@
         <v>259</v>
       </c>
       <c r="B205">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C205">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="D205">
-        <v>53.17460317460318</v>
+        <v>61.01694915254237</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -8919,13 +8901,13 @@
         <v>260</v>
       </c>
       <c r="B206">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C206">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="D206">
-        <v>61.01694915254237</v>
+        <v>53.17460317460318</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -9442,15 +9424,6 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>3393</v>
-      </c>
-      <c r="C8">
-        <v>6392</v>
-      </c>
-      <c r="D8">
-        <v>53.08197747183981</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10149,13 +10122,13 @@
         <v>57</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>43.33333333333334</v>
+        <v>49.12280701754386</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -10163,13 +10136,13 @@
         <v>58</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>41.37931034482759</v>
+        <v>43.33333333333334</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10177,13 +10150,13 @@
         <v>59</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>15.38461538461539</v>
+        <v>41.37931034482759</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10191,13 +10164,13 @@
         <v>60</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
       <c r="D6">
-        <v>81.25</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10205,13 +10178,13 @@
         <v>61</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10219,13 +10192,13 @@
         <v>62</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>69.23076923076923</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10233,13 +10206,13 @@
         <v>63</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>66.66666666666666</v>
+        <v>69.23076923076923</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10247,13 +10220,13 @@
         <v>64</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10261,13 +10234,13 @@
         <v>65</v>
       </c>
       <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
         <v>10</v>
       </c>
-      <c r="C11">
-        <v>19</v>
-      </c>
       <c r="D11">
-        <v>52.63157894736842</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10275,13 +10248,13 @@
         <v>66</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>89.28571428571429</v>
+        <v>52.63157894736842</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10289,13 +10262,13 @@
         <v>67</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>89.28571428571429</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10303,13 +10276,13 @@
         <v>68</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>36.36363636363637</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10320,10 +10293,10 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10331,13 +10304,13 @@
         <v>70</v>
       </c>
       <c r="B16">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>49.12280701754386</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -12968,10 +12941,10 @@
         <v>27</v>
       </c>
       <c r="C205">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="D205">
-        <v>23.47826086956522</v>
+        <v>47.36842105263158</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -12982,10 +12955,10 @@
         <v>27</v>
       </c>
       <c r="C206">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="D206">
-        <v>47.36842105263158</v>
+        <v>23.47826086956522</v>
       </c>
     </row>
     <row r="207" spans="1:4">
